--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E398AAE2-4B2A-4A68-B575-4C3872F6F922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8E5853-C836-4EC7-A6B0-147ADE31240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6680" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29260" yWindow="6340" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>lang_code</t>
   </si>
@@ -65,13 +65,10 @@
     <t>end</t>
   </si>
   <si>
-    <t>UTO</t>
-  </si>
-  <si>
-    <t>Chrustams Day</t>
-  </si>
-  <si>
     <t>Christmas Day</t>
+  </si>
+  <si>
+    <t>ZON1</t>
   </si>
 </sst>
 </file>
@@ -485,16 +482,16 @@
         <v>1000000</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1">
         <v>46381</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>

--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8E5853-C836-4EC7-A6B0-147ADE31240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB2A410-1001-4B02-B1AB-30BEAEDACE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29260" yWindow="6340" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23300" yWindow="11630" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
     <t>Christmas Day</t>
   </si>
   <si>
-    <t>ZON1</t>
+    <t>PRO1</t>
   </si>
 </sst>
 </file>

--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB2A410-1001-4B02-B1AB-30BEAEDACE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210C2082-FCC2-4399-AC6D-D87B4CAC4AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23300" yWindow="11630" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3670" yWindow="5810" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,13 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>end</t>
-  </si>
-  <si>
     <t>Christmas Day</t>
   </si>
   <si>
     <t>PRO1</t>
+  </si>
+  <si>
+    <t>eng</t>
   </si>
 </sst>
 </file>
@@ -476,22 +476,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1000000</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1">
         <v>46381</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
